--- a/output/xlsx/matriz_pruebas_20260812.xlsx
+++ b/output/xlsx/matriz_pruebas_20260812.xlsx
@@ -431,7 +431,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="38" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Registrar reserva asociada al estudiante</t>
+          <t>Registrar reserva del ejemplar</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Registrar reserva asociada al estudiante</t>
+          <t>Registrar reserva del ejemplar</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1216,17 +1216,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Pendiente de relación</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva registrada</t>
+          <t>Mostrar confirmación de reserva</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIS-002</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No evaluado</t>
+          <t>Pendiente de relación</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORREGIR</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+          <t>No se identificó evidencia suficiente para asociarlo a un elemento de diseño.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Registrar Libro</t>
+          <t>Registrar mascota</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
